--- a/UnifacDortmund/Experimental_Data/data/group_contribution.xlsx
+++ b/UnifacDortmund/Experimental_Data/data/group_contribution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Juan\proyectos_personales\Maestría\Materias\Tesis\oleosim\UnifacDortmund\Experimental_Data\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Juan\Maestría\Code\oleosim\UnifacDortmund\Experimental_Data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5429A89F-7F83-4B0C-9676-9E2F1F3F2B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221B5616-AD50-41C3-A2DC-432EFFF86424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4950" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -504,9 +504,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N753"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.90421569230166676</v>
       </c>
@@ -594,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>12.99124001374472</v>
       </c>
@@ -638,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -682,7 +682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.0436952983257639</v>
       </c>
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>0.90421569230166676</v>
       </c>
@@ -770,7 +770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -858,7 +858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>0</v>
       </c>
@@ -946,7 +946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>12.88855175349229</v>
       </c>
@@ -990,7 +990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1.2889959483790709</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>0</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>0</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>15.900232660972449</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1.145124362515882</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>0</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>12.95188544251042</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>2</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>1.4552463095504371</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>0</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>0</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>0</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>13.179052724418201</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>2</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>1.357539365210557</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>0</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>0</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>0</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>0</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>12.74366639656704</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>2</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>1.4914464921594199</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>0</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>0</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>0</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>0</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>13.326537781866</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>2</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1.164598889148063</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>0</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>0</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>0</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>0</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>12.70566613978518</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>2</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>1.5257331543353809</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>0</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>1</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>0</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>0</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>0</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>12.65408035800184</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>2</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>1.5394505262510429</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>0</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>1</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>0</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>0</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>0</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>12.859248872478499</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>2</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>1.4767287845896251</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>0</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>0</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>0</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>0</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>12.789920303087539</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>2</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>1.5277175377842309</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>0</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>0</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>0</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>0</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>11.133217944441</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>2</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>0.18723891827303379</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>0</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>1</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>0</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>0</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>0</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>12</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>2</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>2</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>0</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>1</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>0</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>0</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>0</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>14</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>2</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>1</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>0</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>1</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>0</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>0</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>0</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>14</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>2</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>0</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>0</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>1</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>0</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>0</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>0</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>10</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>2</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>0</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>0</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>1</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>0</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>0</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>0</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>13.674442396701</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>2</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>0.90640295511181912</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>0</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>1</v>
       </c>
@@ -6446,7 +6446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>0</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>0</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>0</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>13.17208607940198</v>
       </c>
@@ -6622,7 +6622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>2</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>1.279842208804453</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>0</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>1</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>0</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>0</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>0</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>13.288595596321681</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>2</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>1.3030439574998629</v>
       </c>
@@ -7062,7 +7062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>0</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>1</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>0</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>0</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>0</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>14</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>2</v>
       </c>
@@ -7370,7 +7370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>1</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>0</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>1</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>0</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>0</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>0.9149194700052542</v>
       </c>
@@ -7634,7 +7634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>13.025416828967311</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>2</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>1.0140687263551771</v>
       </c>
@@ -7766,7 +7766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>0.9149194700052542</v>
       </c>
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>1</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>0</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>0</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>0</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>12.75843701270664</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>2</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>1.5110302607872399</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>0</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>1</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>0</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>0</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>0</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>12.99837355647462</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>2</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>1.364014236928502</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>0</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>1</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>0</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>0</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>0</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>13.39820426215049</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>2</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>1.0320329366378751</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>0</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>1</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>0</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>0</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>0</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>13.85138576450859</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>2</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>0.58779711663340972</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>0</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>1</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>0</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>0</v>
       </c>
@@ -9350,7 +9350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>0</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>13.13351771380986</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>2</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>1.3064814286367361</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>0</v>
       </c>
@@ -9570,7 +9570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>1</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>0</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>0</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>0</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>13.141152477516259</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>2</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>1.2511956088073941</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>0</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>1</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>0</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>0</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>0</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>17.05411199780443</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>2</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>0.59802029560982328</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>0</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>1</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>0</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>0</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>0</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>14.092694996602649</v>
       </c>
@@ -10494,7 +10494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>2</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>1.223277357224446</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>0</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>1</v>
       </c>
@@ -10670,7 +10670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>0</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>0</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>0</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>13.728841274779841</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>2</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>0.86683362208414261</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>0</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>1</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>0</v>
       </c>
@@ -11066,7 +11066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>0</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>5.4182612639773177E-2</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>13.3610523378059</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>2</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>1.0852390346741001</v>
       </c>
@@ -11286,7 +11286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>5.4182612639773177E-2</v>
       </c>
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>1</v>
       </c>
@@ -11374,7 +11374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>0</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>0</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>0</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>13.568538993793849</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>2</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>1.043776501423834</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>0</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>1</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>0</v>
       </c>
@@ -11770,7 +11770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>0</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>0</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>13.51753666100233</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>2</v>
       </c>
@@ -11946,7 +11946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>1.1942872784393179</v>
       </c>
@@ -11990,7 +11990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>0</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>1</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>0</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>0</v>
       </c>
@@ -12166,7 +12166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>0</v>
       </c>
@@ -12210,7 +12210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>12.94804860701996</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>2</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>1.3845795559874541</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>0</v>
       </c>
@@ -12386,7 +12386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>1</v>
       </c>
@@ -12430,7 +12430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>0</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>0</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>13.019978674270879</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>2</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>1.0325573768254439</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>1</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>0</v>
       </c>
@@ -12826,7 +12826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>0</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -12914,7 +12914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>13.019978674270879</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>2</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>1.0325573768254439</v>
       </c>
@@ -13046,7 +13046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>1</v>
       </c>
@@ -13134,7 +13134,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>0</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>0</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>13.019978674270879</v>
       </c>
@@ -13310,7 +13310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>2</v>
       </c>
@@ -13354,7 +13354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>1.0325573768254439</v>
       </c>
@@ -13398,7 +13398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>0.88211491768140882</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>1</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>0</v>
       </c>
@@ -13530,7 +13530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>0</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>0</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>12.81307324391433</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>2</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>1.4618581350147051</v>
       </c>
@@ -13750,7 +13750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>0</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>1</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>0</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>0</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>0</v>
       </c>
@@ -13970,7 +13970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>14</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>2</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>1</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>0</v>
       </c>
@@ -14146,7 +14146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>1</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>0</v>
       </c>
@@ -14234,7 +14234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>0</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>0</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>13.06811299163466</v>
       </c>
@@ -14366,7 +14366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>2</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>1.3432479919342111</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>0</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>1</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>0</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>0</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>0</v>
       </c>
@@ -14674,7 +14674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>12.83699106927911</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>2</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>1.414378586208382</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>0</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>1</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>0</v>
       </c>
@@ -14938,7 +14938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>0</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>0</v>
       </c>
@@ -15026,7 +15026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>12.91991368363948</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>2</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>1.2765285992950259</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>0</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>1</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>0</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>0</v>
       </c>
@@ -15334,7 +15334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>0</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>13.253983338153731</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>2</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>1.1660090149490741</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>0</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>1</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>0</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>0</v>
       </c>
@@ -15686,7 +15686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>0</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>13.28234336837105</v>
       </c>
@@ -15774,7 +15774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>2</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>1.135003564437693</v>
       </c>
@@ -15862,7 +15862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>0</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>1</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>0</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>0</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>0</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>13.06811299163466</v>
       </c>
@@ -16126,7 +16126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>2</v>
       </c>
@@ -16170,7 +16170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>1.3432479919342111</v>
       </c>
@@ -16214,7 +16214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>0</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>1</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>0</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>0</v>
       </c>
@@ -16390,7 +16390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>0</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>13.882210941350451</v>
       </c>
@@ -16478,7 +16478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>2</v>
       </c>
@@ -16522,7 +16522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>0.57358499036138966</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>0</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>1</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>0</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>0</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>0</v>
       </c>
@@ -16786,7 +16786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>13.882210941350451</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>2</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>0.57358499036138966</v>
       </c>
@@ -16918,7 +16918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>0</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>1</v>
       </c>
@@ -17006,7 +17006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>0</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>0</v>
       </c>
@@ -17094,7 +17094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>0</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>13.072969326639109</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>2</v>
       </c>
@@ -17226,7 +17226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>1.4025011860160841</v>
       </c>
@@ -17270,7 +17270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>0</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>1</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>0</v>
       </c>
@@ -17402,7 +17402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>0</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>0</v>
       </c>
@@ -17490,7 +17490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>13.072969326639109</v>
       </c>
@@ -17534,7 +17534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>2</v>
       </c>
@@ -17578,7 +17578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>1.4025011860160841</v>
       </c>
@@ -17622,7 +17622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>0</v>
       </c>
@@ -17666,7 +17666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>1</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>0</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>0</v>
       </c>
@@ -17798,7 +17798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>0</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>13.072969326639109</v>
       </c>
@@ -17886,7 +17886,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>2</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>1.4025011860160841</v>
       </c>
@@ -17974,7 +17974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>0</v>
       </c>
@@ -18018,7 +18018,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>1</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>0</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>0</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>0</v>
       </c>
@@ -18194,7 +18194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>12.11252482206938</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>2</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>0.64375175031452025</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>0</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>1</v>
       </c>
@@ -18414,7 +18414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>0</v>
       </c>
@@ -18458,7 +18458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>0</v>
       </c>
@@ -18502,7 +18502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>0</v>
       </c>
@@ -18546,7 +18546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>13.077414843742259</v>
       </c>
@@ -18590,7 +18590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>2</v>
       </c>
@@ -18634,7 +18634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>1.3262607573658569</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>0</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>1</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>0</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>0</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>0</v>
       </c>
@@ -18898,7 +18898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>12.7732305275222</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>2</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>1.547997760991404</v>
       </c>
@@ -19030,7 +19030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>0</v>
       </c>
@@ -19074,7 +19074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>1</v>
       </c>
@@ -19118,7 +19118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>0</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>0</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>0</v>
       </c>
@@ -19250,7 +19250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>12.864757158717159</v>
       </c>
@@ -19294,7 +19294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>2</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>1.4539417301610831</v>
       </c>
@@ -19382,7 +19382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>0</v>
       </c>
@@ -19426,7 +19426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>1</v>
       </c>
@@ -19470,7 +19470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>0</v>
       </c>
@@ -19514,7 +19514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>0</v>
       </c>
@@ -19558,7 +19558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>0</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>12.834636772928979</v>
       </c>
@@ -19646,7 +19646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>2</v>
       </c>
@@ -19690,7 +19690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>1.4723053611342221</v>
       </c>
@@ -19734,7 +19734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>0</v>
       </c>
@@ -19778,7 +19778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>1</v>
       </c>
@@ -19822,7 +19822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>0</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>0</v>
       </c>
@@ -19910,7 +19910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>0</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>12.71466686734469</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>2</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>1.1929585229442961</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>0</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>1</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>0</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>0</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>0</v>
       </c>
@@ -20306,7 +20306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>13.20853656487486</v>
       </c>
@@ -20350,7 +20350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>2</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>1.171785098475806</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>0</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>1</v>
       </c>
@@ -20526,7 +20526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>0</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>0</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>0</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>12.71371920761699</v>
       </c>
@@ -20702,7 +20702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>2</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>1.5674890908485439</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>0</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>1</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>0</v>
       </c>
@@ -20922,7 +20922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>0</v>
       </c>
@@ -20966,7 +20966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>0</v>
       </c>
@@ -21010,7 +21010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>12.785159536500119</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>2</v>
       </c>
@@ -21098,7 +21098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>1.4854719317364939</v>
       </c>
@@ -21142,7 +21142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>0</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>1</v>
       </c>
@@ -21230,7 +21230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>0</v>
       </c>
@@ -21274,7 +21274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>0</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>0</v>
       </c>
@@ -21362,7 +21362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>13.38796602306693</v>
       </c>
@@ -21406,7 +21406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>2</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>1.134440891232789</v>
       </c>
@@ -21494,7 +21494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>0</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>1</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>0</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>0</v>
       </c>
@@ -21670,7 +21670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>0</v>
       </c>
@@ -21714,7 +21714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>13.821387923647899</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>2</v>
       </c>
@@ -21802,7 +21802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>0.84600536669730619</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>0</v>
       </c>
@@ -21890,7 +21890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>1</v>
       </c>
@@ -21934,7 +21934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>0</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>0</v>
       </c>
@@ -22022,7 +22022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>0</v>
       </c>
@@ -22066,7 +22066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>12.87597603066572</v>
       </c>
@@ -22110,7 +22110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>2</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>1.4591527098797761</v>
       </c>
@@ -22198,7 +22198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>0</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>1</v>
       </c>
@@ -22286,7 +22286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>0</v>
       </c>
@@ -22330,7 +22330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>0</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>0</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>12.60700339919045</v>
       </c>
@@ -22462,7 +22462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>2</v>
       </c>
@@ -22506,7 +22506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>1.626488758689467</v>
       </c>
@@ -22550,7 +22550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>0</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>1</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>0</v>
       </c>
@@ -22682,7 +22682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>0</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>0</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>12.886541480390671</v>
       </c>
@@ -22814,7 +22814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>2</v>
       </c>
@@ -22858,7 +22858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>1.488058263269652</v>
       </c>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>0</v>
       </c>
@@ -22946,7 +22946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>1</v>
       </c>
@@ -22990,7 +22990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>0</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>0</v>
       </c>
@@ -23078,7 +23078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>0</v>
       </c>
@@ -23122,7 +23122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>12.80096282118333</v>
       </c>
@@ -23166,7 +23166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>2</v>
       </c>
@@ -23210,7 +23210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>1.4775123031476891</v>
       </c>
@@ -23254,7 +23254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>0</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>1</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>0</v>
       </c>
@@ -23386,7 +23386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>0</v>
       </c>
@@ -23430,7 +23430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>0</v>
       </c>
@@ -23474,7 +23474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>10.20580781269364</v>
       </c>
@@ -23518,7 +23518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>2</v>
       </c>
@@ -23562,7 +23562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>4.6275882565082457E-2</v>
       </c>
@@ -23606,7 +23606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>0</v>
       </c>
@@ -23650,7 +23650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>1</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>0</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>0</v>
       </c>
@@ -23782,7 +23782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>0</v>
       </c>
@@ -23826,7 +23826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>14.716923986485151</v>
       </c>
@@ -23870,7 +23870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>2</v>
       </c>
@@ -23914,7 +23914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>0.16534818747920321</v>
       </c>
@@ -23958,7 +23958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>0</v>
       </c>
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>1</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>0</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>0</v>
       </c>
@@ -24134,7 +24134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>0</v>
       </c>
@@ -24178,7 +24178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>14.896773031134479</v>
       </c>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>2</v>
       </c>
@@ -24266,7 +24266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>0.18750194781482851</v>
       </c>
@@ -24310,7 +24310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>0</v>
       </c>
@@ -24354,7 +24354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>1</v>
       </c>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>0</v>
       </c>
@@ -24442,7 +24442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>0</v>
       </c>
@@ -24486,7 +24486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>0</v>
       </c>
@@ -24530,7 +24530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>14.55039495657187</v>
       </c>
@@ -24574,7 +24574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>2</v>
       </c>
@@ -24618,7 +24618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>0.15278565398844371</v>
       </c>
@@ -24662,7 +24662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>0</v>
       </c>
@@ -24706,7 +24706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>1</v>
       </c>
@@ -24750,7 +24750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>0</v>
       </c>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>0</v>
       </c>
@@ -24838,7 +24838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>0</v>
       </c>
@@ -24882,7 +24882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>14.716923986485151</v>
       </c>
@@ -24926,7 +24926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>2</v>
       </c>
@@ -24970,7 +24970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>0.16534818747920321</v>
       </c>
@@ -25014,7 +25014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>0</v>
       </c>
@@ -25058,7 +25058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>1</v>
       </c>
@@ -25102,7 +25102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>0</v>
       </c>
@@ -25146,7 +25146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>0</v>
       </c>
@@ -25190,7 +25190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>0</v>
       </c>
@@ -25234,7 +25234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>14.896773031134479</v>
       </c>
@@ -25278,7 +25278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>2</v>
       </c>
@@ -25322,7 +25322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>0.18750194781482851</v>
       </c>
@@ -25366,7 +25366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>0</v>
       </c>
@@ -25410,7 +25410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>1</v>
       </c>
@@ -25454,7 +25454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>0</v>
       </c>
@@ -25498,7 +25498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>0</v>
       </c>
@@ -25542,7 +25542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>0</v>
       </c>
@@ -25586,7 +25586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>14.55039495657187</v>
       </c>
@@ -25630,7 +25630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>2</v>
       </c>
@@ -25674,7 +25674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>0.15278565398844371</v>
       </c>
@@ -25718,7 +25718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>0</v>
       </c>
@@ -25762,7 +25762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>1</v>
       </c>
@@ -25806,7 +25806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>0</v>
       </c>
@@ -25850,7 +25850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>0</v>
       </c>
@@ -25894,7 +25894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>0</v>
       </c>
@@ -25938,7 +25938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>14.716923986485151</v>
       </c>
@@ -25982,7 +25982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="580" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>2</v>
       </c>
@@ -26026,7 +26026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>0.16534818747920321</v>
       </c>
@@ -26070,7 +26070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>0</v>
       </c>
@@ -26114,7 +26114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="583" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>1</v>
       </c>
@@ -26158,7 +26158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="584" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>0</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>0</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="586" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>0</v>
       </c>
@@ -26290,7 +26290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="587" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>14.896773031134479</v>
       </c>
@@ -26334,7 +26334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="588" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>2</v>
       </c>
@@ -26378,7 +26378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>0.18750194781482851</v>
       </c>
@@ -26422,7 +26422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="590" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>0</v>
       </c>
@@ -26466,7 +26466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="591" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>1</v>
       </c>
@@ -26510,7 +26510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="592" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>0</v>
       </c>
@@ -26554,7 +26554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>0</v>
       </c>
@@ -26598,7 +26598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>0</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>14.55039495657187</v>
       </c>
@@ -26686,7 +26686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>2</v>
       </c>
@@ -26730,7 +26730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>0.15278565398844371</v>
       </c>
@@ -26774,7 +26774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>0</v>
       </c>
@@ -26818,7 +26818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>1</v>
       </c>
@@ -26862,7 +26862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>0</v>
       </c>
@@ -26906,7 +26906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>0</v>
       </c>
@@ -26950,7 +26950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A602" s="1">
         <v>0</v>
       </c>
@@ -26994,7 +26994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A603" s="1">
         <v>12.65408035800184</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A604" s="1">
         <v>2</v>
       </c>
@@ -27082,7 +27082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A605" s="1">
         <v>1.5394505262510429</v>
       </c>
@@ -27126,7 +27126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A606" s="1">
         <v>0</v>
       </c>
@@ -27170,7 +27170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A607" s="1">
         <v>1</v>
       </c>
@@ -27214,7 +27214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="608" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A608" s="1">
         <v>0</v>
       </c>
@@ -27258,7 +27258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A609" s="1">
         <v>0</v>
       </c>
@@ -27302,7 +27302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="610" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A610" s="1">
         <v>0.9149194700052542</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A611" s="1">
         <v>13.025416828967311</v>
       </c>
@@ -27390,7 +27390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="612" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A612" s="1">
         <v>2</v>
       </c>
@@ -27434,7 +27434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="613" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A613" s="1">
         <v>1.0140687263551771</v>
       </c>
@@ -27478,7 +27478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="614" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A614" s="1">
         <v>0.9149194700052542</v>
       </c>
@@ -27522,7 +27522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="615" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A615" s="1">
         <v>1</v>
       </c>
@@ -27566,7 +27566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="616" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A616" s="1">
         <v>0</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A617" s="1">
         <v>0</v>
       </c>
@@ -27654,7 +27654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A618" s="1">
         <v>0</v>
       </c>
@@ -27698,7 +27698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="619" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A619" s="1">
         <v>12.51935568848288</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="620" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A620" s="1">
         <v>2</v>
       </c>
@@ -27786,7 +27786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="621" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A621" s="1">
         <v>1.6511728543895561</v>
       </c>
@@ -27830,7 +27830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="622" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A622" s="1">
         <v>0</v>
       </c>
@@ -27874,7 +27874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="623" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A623" s="1">
         <v>1</v>
       </c>
@@ -27918,7 +27918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A624" s="1">
         <v>0</v>
       </c>
@@ -27962,7 +27962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A625" s="1">
         <v>0</v>
       </c>
@@ -28006,7 +28006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A626" s="1">
         <v>0</v>
       </c>
@@ -28050,7 +28050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A627" s="1">
         <v>12.51935568848288</v>
       </c>
@@ -28094,7 +28094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A628" s="1">
         <v>2</v>
       </c>
@@ -28138,7 +28138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A629" s="1">
         <v>1.6511728543895561</v>
       </c>
@@ -28182,7 +28182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="630" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A630" s="1">
         <v>0</v>
       </c>
@@ -28226,7 +28226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="631" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A631" s="1">
         <v>1</v>
       </c>
@@ -28270,7 +28270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A632" s="1">
         <v>0</v>
       </c>
@@ -28314,7 +28314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A633" s="1">
         <v>0</v>
       </c>
@@ -28358,7 +28358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A634" s="1">
         <v>0</v>
       </c>
@@ -28402,7 +28402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A635" s="1">
         <v>13.65645748628984</v>
       </c>
@@ -28446,7 +28446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A636" s="1">
         <v>2</v>
       </c>
@@ -28490,7 +28490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A637" s="1">
         <v>1.0101000577927579</v>
       </c>
@@ -28534,7 +28534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="638" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A638" s="1">
         <v>0</v>
       </c>
@@ -28578,7 +28578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="639" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A639" s="1">
         <v>1</v>
       </c>
@@ -28622,7 +28622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="640" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A640" s="1">
         <v>0</v>
       </c>
@@ -28666,7 +28666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="641" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A641" s="1">
         <v>0</v>
       </c>
@@ -28710,7 +28710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A642" s="1">
         <v>0</v>
       </c>
@@ -28754,7 +28754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="643" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A643" s="1">
         <v>13.726870410035881</v>
       </c>
@@ -28798,7 +28798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="644" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A644" s="1">
         <v>2</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="645" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A645" s="1">
         <v>0.96232889307801039</v>
       </c>
@@ -28886,7 +28886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A646" s="1">
         <v>0</v>
       </c>
@@ -28930,7 +28930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A647" s="1">
         <v>1</v>
       </c>
@@ -28974,7 +28974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A648" s="1">
         <v>0</v>
       </c>
@@ -29018,7 +29018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A649" s="1">
         <v>0</v>
       </c>
@@ -29062,7 +29062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A650" s="1">
         <v>0</v>
       </c>
@@ -29106,7 +29106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A651" s="1">
         <v>12.87758115026992</v>
       </c>
@@ -29150,7 +29150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A652" s="1">
         <v>2</v>
       </c>
@@ -29194,7 +29194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A653" s="1">
         <v>1.4939378241328729</v>
       </c>
@@ -29238,7 +29238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="654" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A654" s="1">
         <v>0</v>
       </c>
@@ -29282,7 +29282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A655" s="1">
         <v>1</v>
       </c>
@@ -29326,7 +29326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="656" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A656" s="1">
         <v>0</v>
       </c>
@@ -29370,7 +29370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A657" s="1">
         <v>0</v>
       </c>
@@ -29414,7 +29414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="658" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A658" s="1">
         <v>0</v>
       </c>
@@ -29458,7 +29458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A659" s="1">
         <v>8</v>
       </c>
@@ -29502,7 +29502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A660" s="1">
         <v>2</v>
       </c>
@@ -29546,7 +29546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A661" s="1">
         <v>0</v>
       </c>
@@ -29590,7 +29590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A662" s="1">
         <v>0</v>
       </c>
@@ -29634,7 +29634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="663" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A663" s="1">
         <v>1</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A664" s="1">
         <v>0</v>
       </c>
@@ -29722,7 +29722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="665" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A665" s="1">
         <v>0</v>
       </c>
@@ -29766,7 +29766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A666" s="1">
         <v>0</v>
       </c>
@@ -29810,7 +29810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="667" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A667" s="1">
         <v>14.352474330799261</v>
       </c>
@@ -29854,7 +29854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A668" s="1">
         <v>2</v>
       </c>
@@ -29898,7 +29898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="669" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A669" s="1">
         <v>0.64140938930347613</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="670" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A670" s="1">
         <v>0</v>
       </c>
@@ -29986,7 +29986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="671" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A671" s="1">
         <v>1</v>
       </c>
@@ -30030,7 +30030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A672" s="1">
         <v>0</v>
       </c>
@@ -30074,7 +30074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="673" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A673" s="1">
         <v>0</v>
       </c>
@@ -30118,7 +30118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A674" s="1">
         <v>0</v>
       </c>
@@ -30162,7 +30162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A675" s="1">
         <v>11.782359511384859</v>
       </c>
@@ -30206,7 +30206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A676" s="1">
         <v>2</v>
       </c>
@@ -30250,7 +30250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A677" s="1">
         <v>2.0332130610430781</v>
       </c>
@@ -30294,7 +30294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A678" s="1">
         <v>0</v>
       </c>
@@ -30338,7 +30338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A679" s="1">
         <v>1</v>
       </c>
@@ -30382,7 +30382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A680" s="1">
         <v>0</v>
       </c>
@@ -30426,7 +30426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A681" s="1">
         <v>0</v>
       </c>
@@ -30470,7 +30470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A682" s="1">
         <v>0</v>
       </c>
@@ -30514,7 +30514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A683" s="1">
         <v>13.99147236529058</v>
       </c>
@@ -30558,7 +30558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A684" s="1">
         <v>2</v>
       </c>
@@ -30602,7 +30602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A685" s="1">
         <v>0.93968079200461707</v>
       </c>
@@ -30646,7 +30646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A686" s="1">
         <v>0</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A687" s="1">
         <v>1</v>
       </c>
@@ -30734,7 +30734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A688" s="1">
         <v>0</v>
       </c>
@@ -30778,7 +30778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="689" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A689" s="1">
         <v>0</v>
       </c>
@@ -30822,7 +30822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A690" s="1">
         <v>0</v>
       </c>
@@ -30866,7 +30866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="691" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A691" s="1">
         <v>12.78825538649768</v>
       </c>
@@ -30910,7 +30910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A692" s="1">
         <v>2</v>
       </c>
@@ -30954,7 +30954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A693" s="1">
         <v>1.526789143739075</v>
       </c>
@@ -30998,7 +30998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A694" s="1">
         <v>0</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A695" s="1">
         <v>1</v>
       </c>
@@ -31086,7 +31086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A696" s="1">
         <v>0</v>
       </c>
@@ -31130,7 +31130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="697" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A697" s="1">
         <v>0</v>
       </c>
@@ -31174,7 +31174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="698" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A698" s="1">
         <v>0</v>
       </c>
@@ -31218,7 +31218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="699" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A699" s="1">
         <v>12.78312066463663</v>
       </c>
@@ -31262,7 +31262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="700" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A700" s="1">
         <v>2</v>
       </c>
@@ -31306,7 +31306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="701" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A701" s="1">
         <v>1.491896177113307</v>
       </c>
@@ -31350,7 +31350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A702" s="1">
         <v>0</v>
       </c>
@@ -31394,7 +31394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="703" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A703" s="1">
         <v>1</v>
       </c>
@@ -31438,7 +31438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A704" s="1">
         <v>0</v>
       </c>
@@ -31482,7 +31482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A705" s="1">
         <v>0</v>
       </c>
@@ -31526,7 +31526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A706" s="1">
         <v>0</v>
       </c>
@@ -31570,7 +31570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A707" s="1">
         <v>12.92222293461186</v>
       </c>
@@ -31614,7 +31614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="708" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A708" s="1">
         <v>2</v>
       </c>
@@ -31658,7 +31658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="709" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A709" s="1">
         <v>1.2706221278410419</v>
       </c>
@@ -31702,7 +31702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="710" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A710" s="1">
         <v>0</v>
       </c>
@@ -31746,7 +31746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A711" s="1">
         <v>1</v>
       </c>
@@ -31790,7 +31790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="712" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A712" s="1">
         <v>0</v>
       </c>
@@ -31834,7 +31834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A713" s="1">
         <v>0</v>
       </c>
@@ -31878,7 +31878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A714" s="1">
         <v>0</v>
       </c>
@@ -31922,7 +31922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="715" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A715" s="1">
         <v>13.31655710958051</v>
       </c>
@@ -31936,10 +31936,10 @@
         <v>41.94967132874153</v>
       </c>
       <c r="E715" s="1">
-        <v>28.633114219161019</v>
+        <v>29.821999999999999</v>
       </c>
       <c r="F715" s="1">
-        <v>15.31655710958051</v>
+        <v>14.911</v>
       </c>
       <c r="G715" s="1">
         <v>13.31655710958051</v>
@@ -31966,7 +31966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A716" s="1">
         <v>2</v>
       </c>
@@ -32010,7 +32010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A717" s="1">
         <v>1.1368143917376741</v>
       </c>
@@ -32024,10 +32024,10 @@
         <v>3.4104431752130222</v>
       </c>
       <c r="E717" s="1">
-        <v>2.2736287834753481</v>
+        <v>2.8559999999999999</v>
       </c>
       <c r="F717" s="1">
-        <v>1.1368143917376741</v>
+        <v>1.4279999999999999</v>
       </c>
       <c r="G717" s="1">
         <v>1.1368143917376741</v>
@@ -32054,7 +32054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A718" s="1">
         <v>0</v>
       </c>
@@ -32098,7 +32098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="719" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A719" s="1">
         <v>1</v>
       </c>
@@ -32142,7 +32142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="720" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A720" s="1">
         <v>0</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A721" s="1">
         <v>0</v>
       </c>
@@ -32230,7 +32230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A722" s="1">
         <v>0</v>
       </c>
@@ -32274,7 +32274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="723" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A723" s="1">
         <v>12.84406077189395</v>
       </c>
@@ -32318,7 +32318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="724" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A724" s="1">
         <v>2</v>
       </c>
@@ -32362,7 +32362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A725" s="1">
         <v>1.511330448649495</v>
       </c>
@@ -32406,7 +32406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="726" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A726" s="1">
         <v>0</v>
       </c>
@@ -32450,7 +32450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A727" s="1">
         <v>1</v>
       </c>
@@ -32494,7 +32494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A728" s="1">
         <v>0</v>
       </c>
@@ -32538,7 +32538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A729" s="1">
         <v>0</v>
       </c>
@@ -32582,7 +32582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="730" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A730" s="1">
         <v>0</v>
       </c>
@@ -32626,7 +32626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A731" s="1">
         <v>12.953539865688089</v>
       </c>
@@ -32670,7 +32670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="732" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A732" s="1">
         <v>2</v>
       </c>
@@ -32714,7 +32714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A733" s="1">
         <v>1.422083436886725</v>
       </c>
@@ -32758,7 +32758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A734" s="1">
         <v>0</v>
       </c>
@@ -32802,7 +32802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="735" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A735" s="1">
         <v>1</v>
       </c>
@@ -32846,7 +32846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="736" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A736" s="1">
         <v>0</v>
       </c>
@@ -32890,7 +32890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A737" s="1">
         <v>0</v>
       </c>
@@ -32934,7 +32934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A738" s="1">
         <v>0</v>
       </c>
@@ -32978,7 +32978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A739" s="1">
         <v>13.062794866280081</v>
       </c>
@@ -33022,7 +33022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="740" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A740" s="1">
         <v>2</v>
       </c>
@@ -33066,7 +33066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A741" s="1">
         <v>1.3330191051951461</v>
       </c>
@@ -33110,7 +33110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="742" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A742" s="1">
         <v>0</v>
       </c>
@@ -33154,7 +33154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="743" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A743" s="1">
         <v>1</v>
       </c>
@@ -33198,7 +33198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A744" s="1">
         <v>0</v>
       </c>
@@ -33242,7 +33242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="745" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A745" s="1">
         <v>0</v>
       </c>
@@ -33286,7 +33286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="746" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A746" s="1">
         <v>0</v>
       </c>
@@ -33330,7 +33330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="747" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A747" s="1">
         <v>10.107057263063201</v>
       </c>
@@ -33374,7 +33374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="748" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A748" s="1">
         <v>2</v>
       </c>
@@ -33418,7 +33418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="749" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A749" s="1">
         <v>8.1272796577987708E-2</v>
       </c>
@@ -33462,7 +33462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="750" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A750" s="1">
         <v>0</v>
       </c>
@@ -33506,7 +33506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A751" s="1">
         <v>1</v>
       </c>
@@ -33550,7 +33550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="752" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A752" s="1">
         <v>0</v>
       </c>
@@ -33594,7 +33594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A753" s="1">
         <v>0</v>
       </c>
